--- a/CFU_A25.xlsx
+++ b/CFU_A25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakamura\Documents\PEC\EC_fig\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE402B77-C033-4F1A-ADC7-DD860E0FF597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5377EBFC-855D-4EE3-B319-9829EA9040D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6C49E1F5-ED29-49F0-BC0E-ACCAF4C7456C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{6C49E1F5-ED29-49F0-BC0E-ACCAF4C7456C}"/>
   </bookViews>
   <sheets>
     <sheet name="liver" sheetId="1" r:id="rId1"/>
@@ -62,8 +62,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0.E+00"/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -104,11 +105,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -425,10 +429,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{225D781E-51D0-4587-B6EE-A58B5A0DDFBC}">
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="4" max="4" width="8.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.25" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -441,7 +445,7 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
@@ -458,7 +462,7 @@
       <c r="C2">
         <v>0.5</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="2">
         <v>13</v>
       </c>
       <c r="E2" s="1">
@@ -476,11 +480,11 @@
       <c r="C3">
         <v>0.5</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="1">
-        <f t="shared" ref="E3:E58" si="0">D3/C3</f>
+        <f t="shared" ref="E3:E61" si="0">D3/C3</f>
         <v>0</v>
       </c>
     </row>
@@ -494,7 +498,7 @@
       <c r="C4">
         <v>0.5</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="2">
         <v>0</v>
       </c>
       <c r="E4" s="1">
@@ -512,7 +516,7 @@
       <c r="C5">
         <v>0.5</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="2">
         <v>0</v>
       </c>
       <c r="E5" s="1">
@@ -530,7 +534,7 @@
       <c r="C6">
         <v>0.5</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="2">
         <v>2</v>
       </c>
       <c r="E6" s="1">
@@ -548,7 +552,7 @@
       <c r="C7">
         <v>0.5</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="1">
@@ -561,17 +565,17 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="D8" s="2">
+        <v>100000</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
@@ -579,12 +583,12 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>0.5</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="2">
         <v>0</v>
       </c>
       <c r="E9" s="1">
@@ -597,12 +601,12 @@
         <v>1</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10">
         <v>0.5</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="2">
         <v>0</v>
       </c>
       <c r="E10" s="1">
@@ -612,15 +616,15 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C11">
         <v>0.5</v>
       </c>
-      <c r="D11" s="1">
+      <c r="D11" s="2">
         <v>0</v>
       </c>
       <c r="E11" s="1">
@@ -633,12 +637,12 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
         <v>0.5</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="2">
         <v>0</v>
       </c>
       <c r="E12" s="1">
@@ -651,17 +655,17 @@
         <v>2</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
         <v>0.5</v>
       </c>
-      <c r="D13" s="1">
-        <v>900</v>
+      <c r="D13" s="2">
+        <v>0</v>
       </c>
       <c r="E13" s="1">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
@@ -669,17 +673,17 @@
         <v>2</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C14">
-        <v>0.36</v>
-      </c>
-      <c r="D14" s="1">
-        <v>6</v>
+        <v>0.5</v>
+      </c>
+      <c r="D14" s="2">
+        <v>900</v>
       </c>
       <c r="E14" s="1">
         <f t="shared" si="0"/>
-        <v>16.666666666666668</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
@@ -687,17 +691,17 @@
         <v>2</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>0.5</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
+        <v>0.36</v>
+      </c>
+      <c r="D15" s="2">
+        <v>6</v>
       </c>
       <c r="E15" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>16.666666666666668</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
@@ -705,17 +709,17 @@
         <v>2</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>0.5</v>
       </c>
-      <c r="D16" s="1">
-        <v>5</v>
+      <c r="D16" s="2">
+        <v>1</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
@@ -723,17 +727,17 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17">
         <v>0.5</v>
       </c>
-      <c r="D17" s="1">
-        <v>0</v>
+      <c r="D17" s="2">
+        <v>5</v>
       </c>
       <c r="E17" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
@@ -741,12 +745,12 @@
         <v>2</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>0.5</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="2">
         <v>0</v>
       </c>
       <c r="E18" s="1">
@@ -759,12 +763,12 @@
         <v>2</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>0.5</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2">
         <v>0</v>
       </c>
       <c r="E19" s="1">
@@ -777,35 +781,35 @@
         <v>2</v>
       </c>
       <c r="B20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20">
         <v>0.5</v>
       </c>
-      <c r="D20" s="1">
-        <v>2</v>
+      <c r="D20" s="2">
+        <v>0</v>
       </c>
       <c r="E20" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C21">
         <v>0.5</v>
       </c>
-      <c r="D21" s="1">
-        <v>13</v>
+      <c r="D21" s="2">
+        <v>2</v>
       </c>
       <c r="E21" s="1">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
@@ -813,17 +817,17 @@
         <v>3</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22">
         <v>0.5</v>
       </c>
-      <c r="D22" s="1">
-        <v>5</v>
+      <c r="D22" s="2">
+        <v>13</v>
       </c>
       <c r="E22" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.4">
@@ -831,17 +835,17 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0.5</v>
       </c>
-      <c r="D23" s="1">
-        <v>1</v>
+      <c r="D23" s="2">
+        <v>5</v>
       </c>
       <c r="E23" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.4">
@@ -849,12 +853,12 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C24">
         <v>0.5</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="1">
@@ -867,17 +871,17 @@
         <v>3</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>0.5</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>8500000</v>
       </c>
       <c r="E25" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>42500000</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
@@ -885,17 +889,17 @@
         <v>3</v>
       </c>
       <c r="B26">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26">
         <v>0.5</v>
       </c>
-      <c r="D26" s="1">
-        <v>21</v>
+      <c r="D26" s="2">
+        <v>1</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="0"/>
-        <v>42</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
@@ -903,12 +907,12 @@
         <v>3</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27">
         <v>0.5</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" s="2">
         <v>0</v>
       </c>
       <c r="E27" s="1">
@@ -921,17 +925,17 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>0.5</v>
       </c>
-      <c r="D28" s="1">
-        <v>8</v>
+      <c r="D28" s="2">
+        <v>21</v>
       </c>
       <c r="E28" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.4">
@@ -939,12 +943,12 @@
         <v>3</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29">
         <v>0.5</v>
       </c>
-      <c r="D29" s="1">
+      <c r="D29" s="2">
         <v>0</v>
       </c>
       <c r="E29" s="1">
@@ -954,33 +958,33 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C30">
         <v>0.5</v>
       </c>
-      <c r="D30" s="1">
-        <v>1</v>
+      <c r="D30" s="2">
+        <v>8</v>
       </c>
       <c r="E30" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C31">
         <v>0.5</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D31" s="2">
         <v>0</v>
       </c>
       <c r="E31" s="1">
@@ -993,17 +997,17 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>0.5</v>
       </c>
-      <c r="D32" s="1">
-        <v>0</v>
+      <c r="D32" s="2">
+        <v>1</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
@@ -1011,17 +1015,17 @@
         <v>4</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>0.5</v>
       </c>
-      <c r="D33" s="1">
-        <v>90</v>
+      <c r="D33" s="2">
+        <v>0</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
@@ -1029,17 +1033,17 @@
         <v>4</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C34">
         <v>0.5</v>
       </c>
-      <c r="D34" s="1">
-        <v>6</v>
+      <c r="D34" s="2">
+        <v>0</v>
       </c>
       <c r="E34" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
@@ -1047,17 +1051,17 @@
         <v>4</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>0.5</v>
       </c>
-      <c r="D35" s="1">
-        <v>0</v>
+      <c r="D35" s="2">
+        <v>90</v>
       </c>
       <c r="E35" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.4">
@@ -1065,17 +1069,17 @@
         <v>4</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>0.5</v>
       </c>
-      <c r="D36" s="1">
-        <v>37</v>
+      <c r="D36" s="2">
+        <v>6</v>
       </c>
       <c r="E36" s="1">
         <f t="shared" si="0"/>
-        <v>74</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.4">
@@ -1083,17 +1087,17 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37">
         <v>0.5</v>
       </c>
-      <c r="D37" s="1">
-        <v>5</v>
+      <c r="D37" s="2">
+        <v>0</v>
       </c>
       <c r="E37" s="1">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.4">
@@ -1101,17 +1105,17 @@
         <v>4</v>
       </c>
       <c r="B38">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38">
         <v>0.5</v>
       </c>
-      <c r="D38" s="1">
-        <v>45</v>
+      <c r="D38" s="2">
+        <v>37</v>
       </c>
       <c r="E38" s="1">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.4">
@@ -1119,53 +1123,53 @@
         <v>4</v>
       </c>
       <c r="B39">
+        <v>8</v>
+      </c>
+      <c r="C39">
+        <v>0.5</v>
+      </c>
+      <c r="D39" s="2">
+        <v>5</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="0"/>
         <v>10</v>
-      </c>
-      <c r="C39">
-        <v>0.5</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0</v>
-      </c>
-      <c r="E39" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C40">
         <v>0.5</v>
       </c>
-      <c r="D40" s="1">
-        <v>0</v>
+      <c r="D40" s="2">
+        <v>45</v>
       </c>
       <c r="E40" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C41">
         <v>0.5</v>
       </c>
-      <c r="D41" s="1">
-        <v>25</v>
+      <c r="D41" s="2">
+        <v>0</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="0"/>
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.4">
@@ -1173,17 +1177,17 @@
         <v>5</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C42">
         <v>0.5</v>
       </c>
-      <c r="D42" s="1">
-        <v>88</v>
+      <c r="D42" s="2">
+        <v>0</v>
       </c>
       <c r="E42" s="1">
         <f t="shared" si="0"/>
-        <v>176</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.4">
@@ -1191,17 +1195,17 @@
         <v>5</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>0.5</v>
       </c>
-      <c r="D43" s="1">
-        <v>0</v>
+      <c r="D43" s="2">
+        <v>25</v>
       </c>
       <c r="E43" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.4">
@@ -1209,17 +1213,17 @@
         <v>5</v>
       </c>
       <c r="B44">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C44">
         <v>0.5</v>
       </c>
-      <c r="D44" s="1">
-        <v>2</v>
+      <c r="D44" s="2">
+        <v>88</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.4">
@@ -1227,12 +1231,12 @@
         <v>5</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C45">
         <v>0.5</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D45" s="2">
         <v>0</v>
       </c>
       <c r="E45" s="1">
@@ -1245,17 +1249,17 @@
         <v>5</v>
       </c>
       <c r="B46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>0.5</v>
       </c>
-      <c r="D46" s="1">
-        <v>8</v>
+      <c r="D46" s="2">
+        <v>2</v>
       </c>
       <c r="E46" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.4">
@@ -1263,12 +1267,12 @@
         <v>5</v>
       </c>
       <c r="B47">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>0.5</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D47" s="2">
         <v>0</v>
       </c>
       <c r="E47" s="1">
@@ -1281,17 +1285,17 @@
         <v>5</v>
       </c>
       <c r="B48">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C48">
         <v>0.5</v>
       </c>
-      <c r="D48" s="1">
-        <v>0</v>
+      <c r="D48" s="2">
+        <v>8</v>
       </c>
       <c r="E48" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.4">
@@ -1299,12 +1303,12 @@
         <v>5</v>
       </c>
       <c r="B49">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49">
         <v>0.5</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D49" s="2">
         <v>0</v>
       </c>
       <c r="E49" s="1">
@@ -1314,33 +1318,33 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A50">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C50">
         <v>0.5</v>
       </c>
-      <c r="D50" s="1">
-        <v>209</v>
+      <c r="D50" s="2">
+        <v>0</v>
       </c>
       <c r="E50" s="1">
         <f t="shared" si="0"/>
-        <v>418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A51">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C51">
         <v>0.5</v>
       </c>
-      <c r="D51" s="1">
+      <c r="D51" s="2">
         <v>0</v>
       </c>
       <c r="E51" s="1">
@@ -1353,17 +1357,17 @@
         <v>6</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52">
         <v>0.5</v>
       </c>
-      <c r="D52" s="1">
-        <v>41</v>
+      <c r="D52" s="2">
+        <v>209</v>
       </c>
       <c r="E52" s="1">
         <f t="shared" si="0"/>
-        <v>82</v>
+        <v>418</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.4">
@@ -1371,12 +1375,12 @@
         <v>6</v>
       </c>
       <c r="B53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C53">
         <v>0.5</v>
       </c>
-      <c r="D53" s="1">
+      <c r="D53" s="2">
         <v>0</v>
       </c>
       <c r="E53" s="1">
@@ -1389,17 +1393,17 @@
         <v>6</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>0.5</v>
       </c>
-      <c r="D54" s="1">
-        <v>36</v>
+      <c r="D54" s="2">
+        <v>41</v>
       </c>
       <c r="E54" s="1">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.4">
@@ -1407,12 +1411,12 @@
         <v>6</v>
       </c>
       <c r="B55">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0.5</v>
       </c>
-      <c r="D55" s="1">
+      <c r="D55" s="2">
         <v>0</v>
       </c>
       <c r="E55" s="1">
@@ -1425,17 +1429,17 @@
         <v>6</v>
       </c>
       <c r="B56">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56">
         <v>0.5</v>
       </c>
-      <c r="D56" s="1">
-        <v>15</v>
+      <c r="D56" s="2">
+        <v>36</v>
       </c>
       <c r="E56" s="1">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.4">
@@ -1443,17 +1447,17 @@
         <v>6</v>
       </c>
       <c r="B57">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C57">
         <v>0.5</v>
       </c>
-      <c r="D57" s="1">
-        <v>7</v>
+      <c r="D57" s="2">
+        <v>0</v>
       </c>
       <c r="E57" s="1">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.4">
@@ -1461,15 +1465,69 @@
         <v>6</v>
       </c>
       <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>0.03</v>
+      </c>
+      <c r="D58" s="2">
+        <v>1040000</v>
+      </c>
+      <c r="E58" s="1">
+        <f t="shared" si="0"/>
+        <v>34666666.666666672</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A59">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>8</v>
+      </c>
+      <c r="C59">
+        <v>0.5</v>
+      </c>
+      <c r="D59" s="2">
+        <v>15</v>
+      </c>
+      <c r="E59" s="1">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A60">
+        <v>6</v>
+      </c>
+      <c r="B60">
+        <v>9</v>
+      </c>
+      <c r="C60">
+        <v>0.5</v>
+      </c>
+      <c r="D60" s="2">
+        <v>7</v>
+      </c>
+      <c r="E60" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A61">
+        <v>6</v>
+      </c>
+      <c r="B61">
         <v>10</v>
       </c>
-      <c r="C58">
-        <v>0.5</v>
-      </c>
-      <c r="D58" s="1">
-        <v>1</v>
-      </c>
-      <c r="E58" s="1">
+      <c r="C61">
+        <v>0.5</v>
+      </c>
+      <c r="D61" s="2">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
@@ -1477,6 +1535,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
